--- a/challenge.xlsx
+++ b/challenge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4649edb1fd06a674/Belgeler/UiPath/UIDemo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B3A8E479FA8C3A2FAC45D062EB23D568B2B3CF46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B3A8E479FA8C3A2FAC45D062EB23D568B2B3CF46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99FF561-7517-4575-9377-43CC5664642A}"/>
   <bookViews>
     <workbookView xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>First Name</t>
   </si>
@@ -100,84 +100,6 @@
     <t>17 Farburn Terrace</t>
   </si>
   <si>
-    <t>Doug</t>
-  </si>
-  <si>
-    <t>Derrick</t>
-  </si>
-  <si>
-    <t>Timepath Inc.</t>
-  </si>
-  <si>
-    <t>99 Shire Oak Road</t>
-  </si>
-  <si>
-    <t>Jessie</t>
-  </si>
-  <si>
-    <t>Marlowe</t>
-  </si>
-  <si>
-    <t>Aperture Inc.</t>
-  </si>
-  <si>
-    <t>Scientist</t>
-  </si>
-  <si>
-    <t>27 Cheshire Street</t>
-  </si>
-  <si>
-    <t>Stan</t>
-  </si>
-  <si>
-    <t>Hamm</t>
-  </si>
-  <si>
-    <t>Sugarwell</t>
-  </si>
-  <si>
-    <t>Advisor</t>
-  </si>
-  <si>
-    <t>10 Dam Road</t>
-  </si>
-  <si>
-    <t>Michelle</t>
-  </si>
-  <si>
-    <t>Norton</t>
-  </si>
-  <si>
-    <t>13 White Rabbit Street</t>
-  </si>
-  <si>
-    <t>Stacy</t>
-  </si>
-  <si>
-    <t>Shelby</t>
-  </si>
-  <si>
-    <t>TechDev</t>
-  </si>
-  <si>
-    <t>HR Manager</t>
-  </si>
-  <si>
-    <t>19 Pineapple Boulevard</t>
-  </si>
-  <si>
-    <t>Lara</t>
-  </si>
-  <si>
-    <t>Palmer</t>
-  </si>
-  <si>
-    <t>Programmer</t>
-  </si>
-  <si>
-    <t>87 Orange Street</t>
-  </si>
-  <si>
     <t>jsmith@itsolutions.co.uk</t>
   </si>
   <si>
@@ -188,24 +110,6 @@
   </si>
   <si>
     <t>mrobertson@mc.com</t>
-  </si>
-  <si>
-    <t>dderrick@timepath.co.uk</t>
-  </si>
-  <si>
-    <t>jmarlowe@aperture.us</t>
-  </si>
-  <si>
-    <t>shamm@sugarwell.org</t>
-  </si>
-  <si>
-    <t>mnorton@aperture.us</t>
-  </si>
-  <si>
-    <t>sshelby@techdev.com</t>
-  </si>
-  <si>
-    <t>lpalmer@timepath.co.uk</t>
   </si>
 </sst>
 </file>
@@ -666,7 +570,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>40716543298</v>
@@ -689,7 +593,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="G3">
         <v>40791345621</v>
@@ -712,7 +616,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G4">
         <v>40735416854</v>
@@ -735,150 +639,18 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="G5">
         <v>40733652145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>40799885412</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>40733154268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>40712462257</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>40731254562</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>40741785214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>40731653845</v>
-      </c>
-    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
